--- a/DateBase/orders/Dang Nguyen 195_2026-7-11.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-7-11.xlsx
@@ -773,6 +773,9 @@
       <c r="G2" t="str">
         <v>05105108310106558105102151012106555105101010301581</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
